--- a/output/yearly_benthic_cover_iteration_87_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_87_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.70484389430821</v>
+        <v>46.03077062841494</v>
       </c>
       <c r="M2" t="n">
-        <v>99.15347368516865</v>
+        <v>98.75056972919597</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.02641020069376</v>
+        <v>88.00760973215743</v>
       </c>
       <c r="C3" t="n">
-        <v>45.91616490386649</v>
+        <v>45.89711293065788</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22873780481931</v>
+        <v>2.228704021266897</v>
       </c>
       <c r="E3" t="n">
-        <v>5.699192618340464</v>
+        <v>5.687324005399019</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429126016064366</v>
+        <v>0.7429013404222991</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96877888088581</v>
+        <v>33.962354030036</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17397967389608</v>
+        <v>34.17346165942575</v>
       </c>
       <c r="I3" t="n">
-        <v>6.569604861105436</v>
+        <v>6.569731297968085</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643203760040228</v>
+        <v>4.643133377639369</v>
       </c>
       <c r="K3" t="n">
-        <v>11.97358979930624</v>
+        <v>11.99239026784257</v>
       </c>
       <c r="L3" t="n">
-        <v>48.87443093241348</v>
+        <v>48.87467432403183</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7641856355862</v>
+        <v>106.7641775225323</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.09979570620445</v>
+        <v>87.15428356981474</v>
       </c>
       <c r="C4" t="n">
-        <v>42.62545253076065</v>
+        <v>42.68041991505486</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184021510052021</v>
+        <v>2.187872486988288</v>
       </c>
       <c r="E4" t="n">
-        <v>6.499207694470037</v>
+        <v>6.497505247962476</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444723990817577</v>
+        <v>0.7444601671181809</v>
       </c>
       <c r="G4" t="n">
-        <v>33.28724607517039</v>
+        <v>33.34013815501308</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24573035776085</v>
+        <v>34.24516768743632</v>
       </c>
       <c r="I4" t="n">
-        <v>5.486165175408397</v>
+        <v>5.486263780807749</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652952494260984</v>
+        <v>4.652876044488631</v>
       </c>
       <c r="K4" t="n">
-        <v>12.90020429379558</v>
+        <v>12.84571643018527</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29185415152417</v>
+        <v>44.2913711187052</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8175109760804</v>
+        <v>99.81750746394533</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.01449003667355</v>
+        <v>86.08508150806421</v>
       </c>
       <c r="C5" t="n">
-        <v>42.39160939471672</v>
+        <v>42.46275507599923</v>
       </c>
       <c r="D5" t="n">
-        <v>2.131321460393152</v>
+        <v>2.13599055277291</v>
       </c>
       <c r="E5" t="n">
-        <v>7.105702744874925</v>
+        <v>7.106759598060647</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457937357604906</v>
+        <v>0.7457804204321038</v>
       </c>
       <c r="G5" t="n">
-        <v>32.48403076199944</v>
+        <v>32.54952953189762</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30651184498256</v>
+        <v>34.30589933987678</v>
       </c>
       <c r="I5" t="n">
-        <v>4.579918640159915</v>
+        <v>4.579994437323497</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661210848503065</v>
+        <v>4.661127627700649</v>
       </c>
       <c r="K5" t="n">
-        <v>13.98550996332645</v>
+        <v>13.91491849193581</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47048716486216</v>
+        <v>43.46993021593141</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84760652290534</v>
+        <v>99.84760378386643</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.74783251496216</v>
+        <v>84.72866961797257</v>
       </c>
       <c r="C6" t="n">
-        <v>41.83629099244993</v>
+        <v>41.81775855158885</v>
       </c>
       <c r="D6" t="n">
-        <v>2.069721199762137</v>
+        <v>2.06977257015817</v>
       </c>
       <c r="E6" t="n">
-        <v>7.537387164653552</v>
+        <v>7.523509388958755</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469149738138455</v>
+        <v>0.7469019110198826</v>
       </c>
       <c r="G6" t="n">
-        <v>31.54516499328712</v>
+        <v>31.54045944127241</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35808879543689</v>
+        <v>34.3574879069146</v>
       </c>
       <c r="I6" t="n">
-        <v>3.822336801672074</v>
+        <v>3.822401455774501</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668218586336534</v>
+        <v>4.668136943874266</v>
       </c>
       <c r="K6" t="n">
-        <v>15.25216748503785</v>
+        <v>15.2713303820274</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78432156028556</v>
+        <v>42.78368899868035</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87278003777334</v>
+        <v>99.8727779322966</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.32060128934957</v>
+        <v>83.24530022467484</v>
       </c>
       <c r="C7" t="n">
-        <v>41.00283721724744</v>
+        <v>40.92816300919124</v>
       </c>
       <c r="D7" t="n">
-        <v>2.000488965583138</v>
+        <v>1.997680213406866</v>
       </c>
       <c r="E7" t="n">
-        <v>7.816818824059468</v>
+        <v>7.79302473448258</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478679871962959</v>
+        <v>0.7478557870416395</v>
       </c>
       <c r="G7" t="n">
-        <v>30.48997830907023</v>
+        <v>30.44187204721563</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40192741102961</v>
+        <v>34.40136620391542</v>
       </c>
       <c r="I7" t="n">
-        <v>3.189344872433983</v>
+        <v>3.189402569602444</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674174919976848</v>
+        <v>4.674098669010247</v>
       </c>
       <c r="K7" t="n">
-        <v>16.67939871065041</v>
+        <v>16.75469977532517</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21158804983349</v>
+        <v>42.21095939726762</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89382397773133</v>
+        <v>99.89382218178403</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.28308878012976</v>
+        <v>88.12653128746143</v>
       </c>
       <c r="C8" t="n">
-        <v>43.30905417411668</v>
+        <v>43.2004173470423</v>
       </c>
       <c r="D8" t="n">
-        <v>2.004809462219747</v>
+        <v>2.001967600770747</v>
       </c>
       <c r="E8" t="n">
-        <v>9.657324186588525</v>
+        <v>9.608142139811193</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494831728728476</v>
+        <v>0.7494608224371194</v>
       </c>
       <c r="G8" t="n">
-        <v>30.9909727960762</v>
+        <v>30.93356278641696</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47622595215099</v>
+        <v>34.4751978321075</v>
       </c>
       <c r="I8" t="n">
-        <v>5.720003379766149</v>
+        <v>5.674069965685921</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684269830455296</v>
+        <v>4.684130140231997</v>
       </c>
       <c r="K8" t="n">
-        <v>11.71691121987025</v>
+        <v>11.87346871253857</v>
       </c>
       <c r="L8" t="n">
-        <v>44.78377872617413</v>
+        <v>44.7373833253387</v>
       </c>
       <c r="M8" t="n">
-        <v>99.80974412016106</v>
+        <v>99.81126938491957</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.50053875533635</v>
+        <v>86.25804233563224</v>
       </c>
       <c r="C9" t="n">
-        <v>42.41448450682034</v>
+        <v>42.21270967061875</v>
       </c>
       <c r="D9" t="n">
-        <v>1.924560007852377</v>
+        <v>1.91754634838404</v>
       </c>
       <c r="E9" t="n">
-        <v>10.06666315986398</v>
+        <v>9.992482930491013</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750862398533414</v>
+        <v>0.7508327646041391</v>
       </c>
       <c r="G9" t="n">
-        <v>29.75045158741955</v>
+        <v>29.62912104110262</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53967033253704</v>
+        <v>34.5383071717904</v>
       </c>
       <c r="I9" t="n">
-        <v>4.775441278296157</v>
+        <v>4.737047300484159</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692889990833836</v>
+        <v>4.69270477877587</v>
       </c>
       <c r="K9" t="n">
-        <v>13.49946124466364</v>
+        <v>13.74195766436777</v>
       </c>
       <c r="L9" t="n">
-        <v>43.92716526574475</v>
+        <v>43.8877196104111</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84111101722873</v>
+        <v>99.84238694539761</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.61564575575076</v>
+        <v>84.28876885426446</v>
       </c>
       <c r="C10" t="n">
-        <v>41.27089988718042</v>
+        <v>40.97863283939241</v>
       </c>
       <c r="D10" t="n">
-        <v>1.840539699184585</v>
+        <v>1.829496040831386</v>
       </c>
       <c r="E10" t="n">
-        <v>10.29148107758805</v>
+        <v>10.19259787758065</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520413666627945</v>
+        <v>0.7520067352567261</v>
       </c>
       <c r="G10" t="n">
-        <v>28.45163933153642</v>
+        <v>28.26860465912184</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59390286648855</v>
+        <v>34.5923098218094</v>
       </c>
       <c r="I10" t="n">
-        <v>3.985782872647901</v>
+        <v>3.953711624309936</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700258541642464</v>
+        <v>4.700042095354538</v>
       </c>
       <c r="K10" t="n">
-        <v>15.38435424424923</v>
+        <v>15.71123114573552</v>
       </c>
       <c r="L10" t="n">
-        <v>43.212094721951</v>
+        <v>43.1785513676364</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86734885338066</v>
+        <v>99.86841535276434</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.6016610913577</v>
+        <v>82.21539163096806</v>
       </c>
       <c r="C11" t="n">
-        <v>39.87529776511317</v>
+        <v>39.51845470398168</v>
       </c>
       <c r="D11" t="n">
-        <v>1.751549697469079</v>
+        <v>1.737670585633444</v>
       </c>
       <c r="E11" t="n">
-        <v>10.3482124357647</v>
+        <v>10.23087553622534</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530507278190017</v>
+        <v>0.7530126278683279</v>
       </c>
       <c r="G11" t="n">
-        <v>27.07600400346167</v>
+        <v>26.84975628082476</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64033347967408</v>
+        <v>34.63858088194308</v>
       </c>
       <c r="I11" t="n">
-        <v>3.325943698300403</v>
+        <v>3.299166794296065</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706567048868759</v>
+        <v>4.70632892417705</v>
       </c>
       <c r="K11" t="n">
-        <v>17.39833890864234</v>
+        <v>17.78460836903193</v>
       </c>
       <c r="L11" t="n">
-        <v>42.6156471353376</v>
+        <v>42.58711160408889</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88928380909309</v>
+        <v>99.89017467710249</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.36202982625618</v>
+        <v>80.0960408475698</v>
       </c>
       <c r="C12" t="n">
-        <v>38.15112222417689</v>
+        <v>37.91018185747251</v>
       </c>
       <c r="D12" t="n">
-        <v>1.653316432453351</v>
+        <v>1.644681320848289</v>
       </c>
       <c r="E12" t="n">
-        <v>10.23031541556654</v>
+        <v>10.1421255370062</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539174607472791</v>
+        <v>0.7538751895734749</v>
       </c>
       <c r="G12" t="n">
-        <v>25.55748341527498</v>
+        <v>25.41292520544327</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68020319437483</v>
+        <v>34.67825872037984</v>
       </c>
       <c r="I12" t="n">
-        <v>2.774809778168686</v>
+        <v>2.752454939484501</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711984129670492</v>
+        <v>4.711719934834218</v>
       </c>
       <c r="K12" t="n">
-        <v>19.63797017374383</v>
+        <v>19.90395915243019</v>
       </c>
       <c r="L12" t="n">
-        <v>42.1185202771265</v>
+        <v>42.09421546803352</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90761267504723</v>
+        <v>99.90835647793622</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>78.11354702171226</v>
+        <v>77.86775075278524</v>
       </c>
       <c r="C13" t="n">
-        <v>36.33194016646613</v>
+        <v>36.10760256634839</v>
       </c>
       <c r="D13" t="n">
-        <v>1.555563371676428</v>
+        <v>1.547683399067814</v>
       </c>
       <c r="E13" t="n">
-        <v>10.01121442390208</v>
+        <v>9.926637301837603</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546621188288586</v>
+        <v>0.7546161349184459</v>
       </c>
       <c r="G13" t="n">
-        <v>24.04638597466506</v>
+        <v>23.91415404531406</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71445746612749</v>
+        <v>34.71234220624851</v>
       </c>
       <c r="I13" t="n">
-        <v>2.314625423831996</v>
+        <v>2.295966822158502</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716638242680364</v>
+        <v>4.716350843240288</v>
       </c>
       <c r="K13" t="n">
-        <v>21.88645297828774</v>
+        <v>22.13224924721477</v>
       </c>
       <c r="L13" t="n">
-        <v>41.70452880585256</v>
+        <v>41.68369110478448</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92292195060642</v>
+        <v>99.92354291834765</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.39108525793249</v>
+        <v>84.37692845603725</v>
       </c>
       <c r="C14" t="n">
-        <v>40.19418727119916</v>
+        <v>39.90263970521703</v>
       </c>
       <c r="D14" t="n">
-        <v>1.557410537315407</v>
+        <v>1.549723595900529</v>
       </c>
       <c r="E14" t="n">
-        <v>12.18908193051438</v>
+        <v>12.10004493339319</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555582481414418</v>
+        <v>0.7556108896914847</v>
       </c>
       <c r="G14" t="n">
-        <v>25.7398654507303</v>
+        <v>25.54986099203029</v>
       </c>
       <c r="H14" t="n">
-        <v>36.4206048253867</v>
+        <v>36.36228360769771</v>
       </c>
       <c r="I14" t="n">
-        <v>3.006325214960246</v>
+        <v>3.336836376752271</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722239050884009</v>
+        <v>4.72256806057178</v>
       </c>
       <c r="K14" t="n">
-        <v>15.6089147420675</v>
+        <v>15.62307154396274</v>
       </c>
       <c r="L14" t="n">
-        <v>44.09680600122941</v>
+        <v>44.36320730207314</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89990801449608</v>
+        <v>99.88891855125291</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.76723367926886</v>
+        <v>83.84066840754652</v>
       </c>
       <c r="C15" t="n">
-        <v>40.03560975678238</v>
+        <v>39.8824298592959</v>
       </c>
       <c r="D15" t="n">
-        <v>1.534334352527176</v>
+        <v>1.530214742832085</v>
       </c>
       <c r="E15" t="n">
-        <v>12.42643788867789</v>
+        <v>12.41168471696947</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563122291516152</v>
+        <v>0.7564471785018423</v>
       </c>
       <c r="G15" t="n">
-        <v>25.3584773213106</v>
+        <v>25.22822396893067</v>
       </c>
       <c r="H15" t="n">
-        <v>36.45694940171146</v>
+        <v>36.40252835709853</v>
       </c>
       <c r="I15" t="n">
-        <v>2.507771053692528</v>
+        <v>2.783774577577411</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726951432197593</v>
+        <v>4.727794865636515</v>
       </c>
       <c r="K15" t="n">
-        <v>16.23276632073114</v>
+        <v>16.15933159245348</v>
       </c>
       <c r="L15" t="n">
-        <v>43.64811488873758</v>
+        <v>43.86554864889639</v>
       </c>
       <c r="M15" t="n">
-        <v>99.9164909662511</v>
+        <v>99.90731010064577</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.54640256253808</v>
+        <v>81.56713707405177</v>
       </c>
       <c r="C16" t="n">
-        <v>38.20303221017156</v>
+        <v>38.03967463173616</v>
       </c>
       <c r="D16" t="n">
-        <v>1.448909748929692</v>
+        <v>1.442765041803609</v>
       </c>
       <c r="E16" t="n">
-        <v>12.08319092097881</v>
+        <v>12.08937598056903</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569588546872916</v>
+        <v>0.7571649841407485</v>
       </c>
       <c r="G16" t="n">
-        <v>23.94663519613053</v>
+        <v>23.78646512175132</v>
       </c>
       <c r="H16" t="n">
-        <v>36.48811906091748</v>
+        <v>36.43707133758386</v>
       </c>
       <c r="I16" t="n">
-        <v>2.091595939098693</v>
+        <v>2.322013457323518</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73099284179557</v>
+        <v>4.732281150879679</v>
       </c>
       <c r="K16" t="n">
-        <v>18.45359743746194</v>
+        <v>18.43286292594824</v>
       </c>
       <c r="L16" t="n">
-        <v>43.27371004531949</v>
+        <v>43.45013537071623</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93033969295298</v>
+        <v>99.92267292840063</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>83.21387158577014</v>
+        <v>83.19877230607885</v>
       </c>
       <c r="C17" t="n">
-        <v>39.41654578572451</v>
+        <v>39.20484309539233</v>
       </c>
       <c r="D17" t="n">
-        <v>1.450125193207962</v>
+        <v>1.444141503844976</v>
       </c>
       <c r="E17" t="n">
-        <v>12.85876161868266</v>
+        <v>12.86442268529149</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575938433810284</v>
+        <v>0.757887353223395</v>
       </c>
       <c r="G17" t="n">
-        <v>24.38313041632026</v>
+        <v>24.17579471764693</v>
       </c>
       <c r="H17" t="n">
-        <v>36.93513493280116</v>
+        <v>36.83847017466001</v>
       </c>
       <c r="I17" t="n">
-        <v>2.094164060245652</v>
+        <v>2.38125991376582</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734961521131424</v>
+        <v>4.73679595764622</v>
       </c>
       <c r="K17" t="n">
-        <v>16.78612841422986</v>
+        <v>16.80122769392117</v>
       </c>
       <c r="L17" t="n">
-        <v>43.72757883987604</v>
+        <v>43.91462953564582</v>
       </c>
       <c r="M17" t="n">
-        <v>99.9302530398304</v>
+        <v>99.92070032495931</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>81.02265979727649</v>
+        <v>81.11138033730927</v>
       </c>
       <c r="C18" t="n">
-        <v>37.5492554025768</v>
+        <v>37.48558483481581</v>
       </c>
       <c r="D18" t="n">
-        <v>1.368984377621601</v>
+        <v>1.366925980251783</v>
       </c>
       <c r="E18" t="n">
-        <v>12.43032303733749</v>
+        <v>12.50758673096295</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581381580782722</v>
+        <v>0.7585059127196778</v>
       </c>
       <c r="G18" t="n">
-        <v>23.0187881527726</v>
+        <v>22.88316055234214</v>
       </c>
       <c r="H18" t="n">
-        <v>36.96167202383517</v>
+        <v>36.86853636518048</v>
       </c>
       <c r="I18" t="n">
-        <v>1.746390559642133</v>
+        <v>1.986002841354236</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738363487989198</v>
+        <v>4.740661954497988</v>
       </c>
       <c r="K18" t="n">
-        <v>18.97734020272352</v>
+        <v>18.88861966269074</v>
       </c>
       <c r="L18" t="n">
-        <v>43.41523317080397</v>
+        <v>43.55964939377775</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9418287761043</v>
+        <v>99.9338538912843</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>80.14854109384626</v>
+        <v>80.33913759314872</v>
       </c>
       <c r="C19" t="n">
-        <v>36.94466926677448</v>
+        <v>37.01977016008187</v>
       </c>
       <c r="D19" t="n">
-        <v>1.337291976564213</v>
+        <v>1.339127746432054</v>
       </c>
       <c r="E19" t="n">
-        <v>12.38525845370421</v>
+        <v>12.52925180509383</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758597308037435</v>
+        <v>0.7590271164204437</v>
       </c>
       <c r="G19" t="n">
-        <v>22.48589626743192</v>
+        <v>22.41780144968521</v>
       </c>
       <c r="H19" t="n">
-        <v>36.98405706015012</v>
+        <v>36.89387040315318</v>
       </c>
       <c r="I19" t="n">
-        <v>1.456206852724389</v>
+        <v>1.656139594736221</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741233175233965</v>
+        <v>4.743919477627776</v>
       </c>
       <c r="K19" t="n">
-        <v>19.85145890615376</v>
+        <v>19.66086240685128</v>
       </c>
       <c r="L19" t="n">
-        <v>43.15536097819281</v>
+        <v>43.26420068747367</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95148915112104</v>
+        <v>99.94483325440682</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.69672437726024</v>
+        <v>78.02804459248948</v>
       </c>
       <c r="C20" t="n">
-        <v>34.71747824091907</v>
+        <v>34.96413450513011</v>
       </c>
       <c r="D20" t="n">
-        <v>1.24738807383248</v>
+        <v>1.254577411252542</v>
       </c>
       <c r="E20" t="n">
-        <v>11.754974546134</v>
+        <v>11.96833042649753</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589924519692424</v>
+        <v>0.7594748886287976</v>
       </c>
       <c r="G20" t="n">
-        <v>20.97420707293239</v>
+        <v>21.00237814028939</v>
       </c>
       <c r="H20" t="n">
-        <v>37.00332159690249</v>
+        <v>36.91563517211566</v>
       </c>
       <c r="I20" t="n">
-        <v>1.214137810681892</v>
+        <v>1.380930499775572</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743702824807762</v>
+        <v>4.746718053929988</v>
       </c>
       <c r="K20" t="n">
-        <v>22.30327562273974</v>
+        <v>21.97195540751053</v>
       </c>
       <c r="L20" t="n">
-        <v>42.93879594598774</v>
+        <v>43.0179062097278</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95954980964656</v>
+        <v>99.95399612236844</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>83.11109241861254</v>
+        <v>83.27114674683591</v>
       </c>
       <c r="C21" t="n">
-        <v>38.00291158228166</v>
+        <v>37.99395560527749</v>
       </c>
       <c r="D21" t="n">
-        <v>1.248298465009375</v>
+        <v>1.255693956588922</v>
       </c>
       <c r="E21" t="n">
-        <v>13.55006488639849</v>
+        <v>13.67019195731661</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595463934779824</v>
+        <v>0.7601508039907277</v>
       </c>
       <c r="G21" t="n">
-        <v>22.47273780515646</v>
+        <v>22.34173264296236</v>
       </c>
       <c r="H21" t="n">
-        <v>38.51355098549678</v>
+        <v>38.26915211129205</v>
       </c>
       <c r="I21" t="n">
-        <v>1.819728923836074</v>
+        <v>2.223282749743187</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747164959237386</v>
+        <v>4.750942524942051</v>
       </c>
       <c r="K21" t="n">
-        <v>16.88890758138746</v>
+        <v>16.7288532531641</v>
       </c>
       <c r="L21" t="n">
-        <v>45.0475674434918</v>
+        <v>45.20314761362128</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93938660716091</v>
+        <v>99.92595647206286</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_87_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_87_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>46.03077062841494</v>
+        <v>45.03438718810014</v>
       </c>
       <c r="M2" t="n">
-        <v>98.75056972919597</v>
+        <v>99.79574550732801</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.00760973215743</v>
+        <v>87.96727953646698</v>
       </c>
       <c r="C3" t="n">
-        <v>45.89711293065788</v>
+        <v>45.84450972965664</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228704021266897</v>
+        <v>2.228640409091792</v>
       </c>
       <c r="E3" t="n">
-        <v>5.687324005399019</v>
+        <v>5.65520950883468</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429013404222991</v>
+        <v>0.7428801363639308</v>
       </c>
       <c r="G3" t="n">
-        <v>33.962354030036</v>
+        <v>33.94448949509069</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17346165942575</v>
+        <v>34.17248627274081</v>
       </c>
       <c r="I3" t="n">
-        <v>6.569731297968085</v>
+        <v>6.5805728620705</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643133377639369</v>
+        <v>4.643000852274567</v>
       </c>
       <c r="K3" t="n">
-        <v>11.99239026784257</v>
+        <v>12.03272046353302</v>
       </c>
       <c r="L3" t="n">
-        <v>48.87467432403183</v>
+        <v>48.8865514259455</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7641775225323</v>
+        <v>106.7637816191352</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.15428356981474</v>
+        <v>87.13941474461471</v>
       </c>
       <c r="C4" t="n">
-        <v>42.68041991505486</v>
+        <v>42.65732321059419</v>
       </c>
       <c r="D4" t="n">
-        <v>2.187872486988288</v>
+        <v>2.189123406629867</v>
       </c>
       <c r="E4" t="n">
-        <v>6.497505247962476</v>
+        <v>6.470824232908649</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444601671181809</v>
+        <v>0.7444417633011685</v>
       </c>
       <c r="G4" t="n">
-        <v>33.34013815501308</v>
+        <v>33.34260483506474</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24516768743632</v>
+        <v>34.24432111185374</v>
       </c>
       <c r="I4" t="n">
-        <v>5.486263780807749</v>
+        <v>5.495338374224246</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652876044488631</v>
+        <v>4.652761020632303</v>
       </c>
       <c r="K4" t="n">
-        <v>12.84571643018527</v>
+        <v>12.86058525538527</v>
       </c>
       <c r="L4" t="n">
-        <v>44.2913711187052</v>
+        <v>44.29929784340747</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81750746394533</v>
+        <v>99.81720630938693</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.08508150806421</v>
+        <v>86.09667042404944</v>
       </c>
       <c r="C5" t="n">
-        <v>42.46275507599923</v>
+        <v>42.4674913582036</v>
       </c>
       <c r="D5" t="n">
-        <v>2.13599055277291</v>
+        <v>2.138568459046242</v>
       </c>
       <c r="E5" t="n">
-        <v>7.106759598060647</v>
+        <v>7.085986055314888</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457804204321038</v>
+        <v>0.7457639932595557</v>
       </c>
       <c r="G5" t="n">
-        <v>32.54952953189762</v>
+        <v>32.5726008989535</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30589933987678</v>
+        <v>34.30514368993956</v>
       </c>
       <c r="I5" t="n">
-        <v>4.579994437323497</v>
+        <v>4.587582369663465</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661127627700649</v>
+        <v>4.661024957872223</v>
       </c>
       <c r="K5" t="n">
-        <v>13.91491849193581</v>
+        <v>13.90332957595057</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46993021593141</v>
+        <v>43.47653077767292</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84760378386643</v>
+        <v>99.84735171182709</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.72866961797257</v>
+        <v>84.7766869558321</v>
       </c>
       <c r="C6" t="n">
-        <v>41.81775855158885</v>
+        <v>41.86010015636568</v>
       </c>
       <c r="D6" t="n">
-        <v>2.06977257015817</v>
+        <v>2.074148743388974</v>
       </c>
       <c r="E6" t="n">
-        <v>7.523509388958755</v>
+        <v>7.510659582209938</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469019110198826</v>
+        <v>0.7468866827305211</v>
       </c>
       <c r="G6" t="n">
-        <v>31.54045944127241</v>
+        <v>31.5914222608546</v>
       </c>
       <c r="H6" t="n">
-        <v>34.3574879069146</v>
+        <v>34.35678740560396</v>
       </c>
       <c r="I6" t="n">
-        <v>3.822401455774501</v>
+        <v>3.828740513978353</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668136943874266</v>
+        <v>4.668041767065756</v>
       </c>
       <c r="K6" t="n">
-        <v>15.2713303820274</v>
+        <v>15.2233130441679</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78368899868035</v>
+        <v>42.78915395586466</v>
       </c>
       <c r="M6" t="n">
-        <v>99.8727779322966</v>
+        <v>99.87256715639823</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.24530022467484</v>
+        <v>83.33417959438316</v>
       </c>
       <c r="C7" t="n">
-        <v>40.92816300919124</v>
+        <v>41.01237942356541</v>
       </c>
       <c r="D7" t="n">
-        <v>1.997680213406866</v>
+        <v>2.004043702434019</v>
       </c>
       <c r="E7" t="n">
-        <v>7.79302473448258</v>
+        <v>7.789252630342629</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478557870416395</v>
+        <v>0.7478411028811309</v>
       </c>
       <c r="G7" t="n">
-        <v>30.44187204721563</v>
+        <v>30.52365026114555</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40136620391542</v>
+        <v>34.40069073253201</v>
       </c>
       <c r="I7" t="n">
-        <v>3.189402569602444</v>
+        <v>3.194694272040733</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674098669010247</v>
+        <v>4.674006893007068</v>
       </c>
       <c r="K7" t="n">
-        <v>16.75469977532517</v>
+        <v>16.66582040561686</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21095939726762</v>
+        <v>42.21544626765168</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89382218178403</v>
+        <v>99.89364609683393</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.12653128746143</v>
+        <v>88.10372033067129</v>
       </c>
       <c r="C8" t="n">
-        <v>43.2004173470423</v>
+        <v>43.27553296930783</v>
       </c>
       <c r="D8" t="n">
-        <v>2.001967600770747</v>
+        <v>2.00827426794798</v>
       </c>
       <c r="E8" t="n">
-        <v>9.608142139811193</v>
+        <v>9.592617714885399</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494608224371194</v>
+        <v>0.7494198063674514</v>
       </c>
       <c r="G8" t="n">
-        <v>30.93356278641696</v>
+        <v>31.01657646200822</v>
       </c>
       <c r="H8" t="n">
-        <v>34.4751978321075</v>
+        <v>34.47331109290275</v>
       </c>
       <c r="I8" t="n">
-        <v>5.674069965685921</v>
+        <v>5.57964719676293</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684130140231997</v>
+        <v>4.683873789796571</v>
       </c>
       <c r="K8" t="n">
-        <v>11.87346871253857</v>
+        <v>11.8962796693287</v>
       </c>
       <c r="L8" t="n">
-        <v>44.7373833253387</v>
+        <v>44.64259091827235</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81126938491957</v>
+        <v>99.81440355690889</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.25804233563224</v>
+        <v>86.09167689790695</v>
       </c>
       <c r="C9" t="n">
-        <v>42.21270967061875</v>
+        <v>42.1297958179951</v>
       </c>
       <c r="D9" t="n">
-        <v>1.91754634838404</v>
+        <v>1.916911212531128</v>
       </c>
       <c r="E9" t="n">
-        <v>9.992482930491013</v>
+        <v>9.932566382364923</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508327646041391</v>
+        <v>0.7507714145114059</v>
       </c>
       <c r="G9" t="n">
-        <v>29.62912104110262</v>
+        <v>29.6055295550362</v>
       </c>
       <c r="H9" t="n">
-        <v>34.5383071717904</v>
+        <v>34.53548506752466</v>
       </c>
       <c r="I9" t="n">
-        <v>4.737047300484159</v>
+        <v>4.658091925242364</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69270477877587</v>
+        <v>4.692321340696286</v>
       </c>
       <c r="K9" t="n">
-        <v>13.74195766436777</v>
+        <v>13.90832310209306</v>
       </c>
       <c r="L9" t="n">
-        <v>43.8877196104111</v>
+        <v>43.80689088000177</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84238694539761</v>
+        <v>99.84500980008991</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.28876885426446</v>
+        <v>83.96699356082704</v>
       </c>
       <c r="C10" t="n">
-        <v>40.97863283939241</v>
+        <v>40.72805243920297</v>
       </c>
       <c r="D10" t="n">
-        <v>1.829496040831386</v>
+        <v>1.821471081412577</v>
       </c>
       <c r="E10" t="n">
-        <v>10.19259787758065</v>
+        <v>10.08599451396809</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520067352567261</v>
+        <v>0.7519301236557216</v>
       </c>
       <c r="G10" t="n">
-        <v>28.26860465912184</v>
+        <v>28.13151468982194</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5923098218094</v>
+        <v>34.58878568816318</v>
       </c>
       <c r="I10" t="n">
-        <v>3.953711624309936</v>
+        <v>3.887734190957264</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700042095354538</v>
+        <v>4.699563272848259</v>
       </c>
       <c r="K10" t="n">
-        <v>15.71123114573552</v>
+        <v>16.03300643917296</v>
       </c>
       <c r="L10" t="n">
-        <v>43.1785513676364</v>
+        <v>43.10954967925625</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86841535276434</v>
+        <v>99.87060855763218</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.21539163096806</v>
+        <v>81.54130024776218</v>
       </c>
       <c r="C11" t="n">
-        <v>39.51845470398168</v>
+        <v>38.90518017787087</v>
       </c>
       <c r="D11" t="n">
-        <v>1.737670585633444</v>
+        <v>1.713389562234372</v>
       </c>
       <c r="E11" t="n">
-        <v>10.23087553622534</v>
+        <v>10.02819608444374</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530126278683279</v>
+        <v>0.7529272942702667</v>
       </c>
       <c r="G11" t="n">
-        <v>26.84975628082476</v>
+        <v>26.46226126302473</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63858088194308</v>
+        <v>34.63465553643226</v>
       </c>
       <c r="I11" t="n">
-        <v>3.299166794296065</v>
+        <v>3.244074918167634</v>
       </c>
       <c r="J11" t="n">
-        <v>4.70632892417705</v>
+        <v>4.705795589189166</v>
       </c>
       <c r="K11" t="n">
-        <v>17.78460836903193</v>
+        <v>18.45869975223782</v>
       </c>
       <c r="L11" t="n">
-        <v>42.58711160408889</v>
+        <v>42.52812745347583</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89017467710249</v>
+        <v>99.89200738358453</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.0960408475698</v>
+        <v>79.07743849491035</v>
       </c>
       <c r="C12" t="n">
-        <v>37.91018185747251</v>
+        <v>36.94347841197791</v>
       </c>
       <c r="D12" t="n">
-        <v>1.644681320848289</v>
+        <v>1.604717444746846</v>
       </c>
       <c r="E12" t="n">
-        <v>10.1421255370062</v>
+        <v>9.843235489251386</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538751895734749</v>
+        <v>0.7537862761600772</v>
       </c>
       <c r="G12" t="n">
-        <v>25.41292520544327</v>
+        <v>24.78388640400497</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67825872037984</v>
+        <v>34.67416870336353</v>
       </c>
       <c r="I12" t="n">
-        <v>2.752454939484501</v>
+        <v>2.706479951383064</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711719934834218</v>
+        <v>4.711164226000482</v>
       </c>
       <c r="K12" t="n">
-        <v>19.90395915243019</v>
+        <v>20.92256150508963</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09421546803352</v>
+        <v>42.04384689076112</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90835647793622</v>
+        <v>99.90988680782867</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.86775075278524</v>
+        <v>76.67908905807059</v>
       </c>
       <c r="C13" t="n">
-        <v>36.10760256634839</v>
+        <v>34.96317617057116</v>
       </c>
       <c r="D13" t="n">
-        <v>1.547683399067814</v>
+        <v>1.499964573861444</v>
       </c>
       <c r="E13" t="n">
-        <v>9.926637301837603</v>
+        <v>9.576956899034805</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546161349184459</v>
+        <v>0.754526051086965</v>
       </c>
       <c r="G13" t="n">
-        <v>23.91415404531406</v>
+        <v>23.1660419286327</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71234220624851</v>
+        <v>34.70819835000037</v>
       </c>
       <c r="I13" t="n">
-        <v>2.295966822158502</v>
+        <v>2.257613436160775</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716350843240288</v>
+        <v>4.71578781929353</v>
       </c>
       <c r="K13" t="n">
-        <v>22.13224924721477</v>
+        <v>23.32091094192941</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68369110478448</v>
+        <v>41.6407328888499</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92354291834765</v>
+        <v>99.92482000135047</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.37692845603725</v>
+        <v>83.54997291231903</v>
       </c>
       <c r="C14" t="n">
-        <v>39.90263970521703</v>
+        <v>39.15937650376276</v>
       </c>
       <c r="D14" t="n">
-        <v>1.549723595900529</v>
+        <v>1.501784537137961</v>
       </c>
       <c r="E14" t="n">
-        <v>12.10004493339319</v>
+        <v>11.92548118203703</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556108896914847</v>
+        <v>0.7554415458446971</v>
       </c>
       <c r="G14" t="n">
-        <v>25.54986099203029</v>
+        <v>25.0241827790027</v>
       </c>
       <c r="H14" t="n">
-        <v>36.36228360769771</v>
+        <v>36.58034373166716</v>
       </c>
       <c r="I14" t="n">
-        <v>3.336836376752271</v>
+        <v>3.041229475100137</v>
       </c>
       <c r="J14" t="n">
-        <v>4.72256806057178</v>
+        <v>4.721509661529355</v>
       </c>
       <c r="K14" t="n">
-        <v>15.62307154396274</v>
+        <v>16.45002708768096</v>
       </c>
       <c r="L14" t="n">
-        <v>44.36320730207314</v>
+        <v>44.28934494491806</v>
       </c>
       <c r="M14" t="n">
-        <v>99.88891855125291</v>
+        <v>99.89874853636178</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.84066840754652</v>
+        <v>82.80435516589769</v>
       </c>
       <c r="C15" t="n">
-        <v>39.8824298592959</v>
+        <v>38.88366528025382</v>
       </c>
       <c r="D15" t="n">
-        <v>1.530214742832085</v>
+        <v>1.474167183948042</v>
       </c>
       <c r="E15" t="n">
-        <v>12.41168471696947</v>
+        <v>12.12899962741993</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564471785018423</v>
+        <v>0.7562130489489157</v>
       </c>
       <c r="G15" t="n">
-        <v>25.22822396893067</v>
+        <v>24.56399579677828</v>
       </c>
       <c r="H15" t="n">
-        <v>36.40252835709853</v>
+        <v>36.61770181568782</v>
       </c>
       <c r="I15" t="n">
-        <v>2.783774577577411</v>
+        <v>2.536946137183965</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727794865636515</v>
+        <v>4.726331555930721</v>
       </c>
       <c r="K15" t="n">
-        <v>16.15933159245348</v>
+        <v>17.19564483410233</v>
       </c>
       <c r="L15" t="n">
-        <v>43.86554864889639</v>
+        <v>43.83621128911329</v>
       </c>
       <c r="M15" t="n">
-        <v>99.90731010064577</v>
+        <v>99.91552140346943</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.56713707405177</v>
+        <v>80.51187610171097</v>
       </c>
       <c r="C16" t="n">
-        <v>38.03967463173616</v>
+        <v>36.98325022307289</v>
       </c>
       <c r="D16" t="n">
-        <v>1.442765041803609</v>
+        <v>1.386836426136012</v>
       </c>
       <c r="E16" t="n">
-        <v>12.08937598056903</v>
+        <v>11.76313099945607</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7571649841407485</v>
+        <v>0.7568755296992967</v>
       </c>
       <c r="G16" t="n">
-        <v>23.78646512175132</v>
+        <v>23.10880645924398</v>
       </c>
       <c r="H16" t="n">
-        <v>36.43707133758386</v>
+        <v>36.6497807683187</v>
       </c>
       <c r="I16" t="n">
-        <v>2.322013457323518</v>
+        <v>2.115973858236311</v>
       </c>
       <c r="J16" t="n">
-        <v>4.732281150879679</v>
+        <v>4.730472060620603</v>
       </c>
       <c r="K16" t="n">
-        <v>18.43286292594824</v>
+        <v>19.48812389828905</v>
       </c>
       <c r="L16" t="n">
-        <v>43.45013537071623</v>
+        <v>43.45815515260517</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92267292840063</v>
+        <v>99.92952927396712</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>83.19877230607885</v>
+        <v>82.1751923321541</v>
       </c>
       <c r="C17" t="n">
-        <v>39.20484309539233</v>
+        <v>38.19552706912143</v>
       </c>
       <c r="D17" t="n">
-        <v>1.444141503844976</v>
+        <v>1.388027379485003</v>
       </c>
       <c r="E17" t="n">
-        <v>12.86442268529149</v>
+        <v>12.54009907999933</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757887353223395</v>
+        <v>0.7575255006907397</v>
       </c>
       <c r="G17" t="n">
-        <v>24.17579471764693</v>
+        <v>23.54267572625217</v>
       </c>
       <c r="H17" t="n">
-        <v>36.83847017466001</v>
+        <v>37.09527842090871</v>
       </c>
       <c r="I17" t="n">
-        <v>2.38125991376582</v>
+        <v>2.117051845501007</v>
       </c>
       <c r="J17" t="n">
-        <v>4.73679595764622</v>
+        <v>4.734534379317121</v>
       </c>
       <c r="K17" t="n">
-        <v>16.80122769392117</v>
+        <v>17.82480766784594</v>
       </c>
       <c r="L17" t="n">
-        <v>43.91462953564582</v>
+        <v>43.90915741718001</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92070032495931</v>
+        <v>99.92949215414737</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>81.11138033730927</v>
+        <v>79.94797003786861</v>
       </c>
       <c r="C18" t="n">
-        <v>37.48558483481581</v>
+        <v>36.29514037068361</v>
       </c>
       <c r="D18" t="n">
-        <v>1.366925980251783</v>
+        <v>1.306485600979036</v>
       </c>
       <c r="E18" t="n">
-        <v>12.50758673096295</v>
+        <v>12.09766331574992</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7585059127196778</v>
+        <v>0.7580831207379615</v>
       </c>
       <c r="G18" t="n">
-        <v>22.88316055234214</v>
+        <v>22.15962545081732</v>
       </c>
       <c r="H18" t="n">
-        <v>36.86853636518048</v>
+        <v>37.12258452596512</v>
       </c>
       <c r="I18" t="n">
-        <v>1.986002841354236</v>
+        <v>1.765508519007013</v>
       </c>
       <c r="J18" t="n">
-        <v>4.740661954497988</v>
+        <v>4.738019504612257</v>
       </c>
       <c r="K18" t="n">
-        <v>18.88861966269074</v>
+        <v>20.05202996213138</v>
       </c>
       <c r="L18" t="n">
-        <v>43.55964939377775</v>
+        <v>43.59402267147667</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9338538912843</v>
+        <v>99.94119300429166</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>80.33913759314872</v>
+        <v>79.06408294478115</v>
       </c>
       <c r="C19" t="n">
-        <v>37.01977016008187</v>
+        <v>35.6831799117255</v>
       </c>
       <c r="D19" t="n">
-        <v>1.339127746432054</v>
+        <v>1.274805494146095</v>
       </c>
       <c r="E19" t="n">
-        <v>12.52925180509383</v>
+        <v>12.04967677414006</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7590271164204437</v>
+        <v>0.758553636713337</v>
       </c>
       <c r="G19" t="n">
-        <v>22.41780144968521</v>
+        <v>21.62229132242448</v>
       </c>
       <c r="H19" t="n">
-        <v>36.89387040315318</v>
+        <v>37.14562523032705</v>
       </c>
       <c r="I19" t="n">
-        <v>1.656139594736221</v>
+        <v>1.472170257571779</v>
       </c>
       <c r="J19" t="n">
-        <v>4.743919477627776</v>
+        <v>4.740960229458354</v>
       </c>
       <c r="K19" t="n">
-        <v>19.66086240685128</v>
+        <v>20.93591705521887</v>
       </c>
       <c r="L19" t="n">
-        <v>43.26420068747367</v>
+        <v>43.33186112974988</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94483325440682</v>
+        <v>99.95095809669424</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>78.02804459248948</v>
+        <v>76.63556310121693</v>
       </c>
       <c r="C20" t="n">
-        <v>34.96413450513011</v>
+        <v>33.48127547518917</v>
       </c>
       <c r="D20" t="n">
-        <v>1.254577411252542</v>
+        <v>1.186850076733425</v>
       </c>
       <c r="E20" t="n">
-        <v>11.96833042649753</v>
+        <v>11.42288457410357</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7594748886287976</v>
+        <v>0.7589586257688854</v>
       </c>
       <c r="G20" t="n">
-        <v>21.00237814028939</v>
+        <v>20.13045773101368</v>
       </c>
       <c r="H20" t="n">
-        <v>36.91563517211566</v>
+        <v>37.16545714589859</v>
       </c>
       <c r="I20" t="n">
-        <v>1.380930499775572</v>
+        <v>1.227463536643251</v>
       </c>
       <c r="J20" t="n">
-        <v>4.746718053929988</v>
+        <v>4.743491411055532</v>
       </c>
       <c r="K20" t="n">
-        <v>21.97195540751053</v>
+        <v>23.36443689878308</v>
       </c>
       <c r="L20" t="n">
-        <v>43.0179062097278</v>
+        <v>43.11339400776188</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95399612236844</v>
+        <v>99.95910638173413</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>83.27114674683591</v>
+        <v>82.18294813901761</v>
       </c>
       <c r="C21" t="n">
-        <v>37.99395560527749</v>
+        <v>36.86322624761313</v>
       </c>
       <c r="D21" t="n">
-        <v>1.255693956588922</v>
+        <v>1.18772671121919</v>
       </c>
       <c r="E21" t="n">
-        <v>13.67019195731661</v>
+        <v>13.26635727902472</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7601508039907277</v>
+        <v>0.7595192098878578</v>
       </c>
       <c r="G21" t="n">
-        <v>22.34173264296236</v>
+        <v>21.67685106559312</v>
       </c>
       <c r="H21" t="n">
-        <v>38.26915211129205</v>
+        <v>38.72443291885406</v>
       </c>
       <c r="I21" t="n">
-        <v>2.223282749743187</v>
+        <v>1.821065892639563</v>
       </c>
       <c r="J21" t="n">
-        <v>4.750942524942051</v>
+        <v>4.746995061799109</v>
       </c>
       <c r="K21" t="n">
-        <v>16.7288532531641</v>
+        <v>17.81705186098239</v>
       </c>
       <c r="L21" t="n">
-        <v>45.20314761362128</v>
+        <v>45.25906449791488</v>
       </c>
       <c r="M21" t="n">
-        <v>99.92595647206286</v>
+        <v>99.93934260651041</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_87_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_87_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.03438718810014</v>
+        <v>44.27128984091707</v>
       </c>
       <c r="M2" t="n">
-        <v>99.79574550732801</v>
+        <v>93.58744836660006</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.96727953646698</v>
+        <v>81.48535317651351</v>
       </c>
       <c r="C3" t="n">
-        <v>45.84450972965664</v>
+        <v>43.24090873206906</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228640409091792</v>
+        <v>2.180913011379311</v>
       </c>
       <c r="E3" t="n">
-        <v>5.65520950883468</v>
+        <v>4.147104285217966</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428801363639308</v>
+        <v>0.7376389434035253</v>
       </c>
       <c r="G3" t="n">
-        <v>33.94448949509069</v>
+        <v>32.80456654616381</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17248627274081</v>
+        <v>33.93139139656216</v>
       </c>
       <c r="I3" t="n">
-        <v>6.5805728620705</v>
+        <v>3.073495597514689</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643000852274567</v>
+        <v>4.610243396272033</v>
       </c>
       <c r="K3" t="n">
-        <v>12.03272046353302</v>
+        <v>18.5146468234865</v>
       </c>
       <c r="L3" t="n">
-        <v>48.8865514259455</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7637816191352</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.13941474461471</v>
+        <v>88.71168885752846</v>
       </c>
       <c r="C4" t="n">
-        <v>42.65732321059419</v>
+        <v>42.90131239005596</v>
       </c>
       <c r="D4" t="n">
-        <v>2.189123406629867</v>
+        <v>2.186692700095212</v>
       </c>
       <c r="E4" t="n">
-        <v>6.470824232908649</v>
+        <v>6.576004412248018</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444417633011685</v>
+        <v>0.7395937776657605</v>
       </c>
       <c r="G4" t="n">
-        <v>33.34260483506474</v>
+        <v>33.51271527408767</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24432111185374</v>
+        <v>34.02131377262498</v>
       </c>
       <c r="I4" t="n">
-        <v>5.495338374224246</v>
+        <v>7.052907810395823</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652761020632303</v>
+        <v>4.622461110411002</v>
       </c>
       <c r="K4" t="n">
-        <v>12.86058525538527</v>
+        <v>11.28831114247155</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29929784340747</v>
+        <v>45.57590092958092</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81720630938693</v>
+        <v>99.76552446210843</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.09667042404944</v>
+        <v>87.72434291258602</v>
       </c>
       <c r="C5" t="n">
-        <v>42.4674913582036</v>
+        <v>43.00723074837589</v>
       </c>
       <c r="D5" t="n">
-        <v>2.138568459046242</v>
+        <v>2.140402445743526</v>
       </c>
       <c r="E5" t="n">
-        <v>7.085986055314888</v>
+        <v>7.418559597203255</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457639932595557</v>
+        <v>0.7412492038583103</v>
       </c>
       <c r="G5" t="n">
-        <v>32.5726008989535</v>
+        <v>32.80328220469222</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30514368993956</v>
+        <v>34.09746337748226</v>
       </c>
       <c r="I5" t="n">
-        <v>4.587582369663465</v>
+        <v>5.890578559492018</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661024957872223</v>
+        <v>4.632807524114439</v>
       </c>
       <c r="K5" t="n">
-        <v>13.90332957595057</v>
+        <v>12.27565708741396</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47653077767292</v>
+        <v>44.52119805836583</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84735171182709</v>
+        <v>99.80408589415568</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.7766869558321</v>
+        <v>86.56853715497297</v>
       </c>
       <c r="C6" t="n">
-        <v>41.86010015636568</v>
+        <v>42.7658236049248</v>
       </c>
       <c r="D6" t="n">
-        <v>2.074148743388974</v>
+        <v>2.085946738218381</v>
       </c>
       <c r="E6" t="n">
-        <v>7.510659582209938</v>
+        <v>8.049503266059846</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468866827305211</v>
+        <v>0.7426529263849534</v>
       </c>
       <c r="G6" t="n">
-        <v>31.5914222608546</v>
+        <v>31.96870740538013</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35678740560396</v>
+        <v>34.16203461370785</v>
       </c>
       <c r="I6" t="n">
-        <v>3.828740513978353</v>
+        <v>4.918111415315852</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668041767065756</v>
+        <v>4.641580789905958</v>
       </c>
       <c r="K6" t="n">
-        <v>15.2233130441679</v>
+        <v>13.43146284502703</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78915395586466</v>
+        <v>43.63908636784005</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87256715639823</v>
+        <v>99.83637281779188</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.33417959438316</v>
+        <v>85.2933743749753</v>
       </c>
       <c r="C7" t="n">
-        <v>41.01237942356541</v>
+        <v>42.25471858595064</v>
       </c>
       <c r="D7" t="n">
-        <v>2.004043702434019</v>
+        <v>2.026017007048647</v>
       </c>
       <c r="E7" t="n">
-        <v>7.789252630342629</v>
+        <v>8.502406038039856</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478411028811309</v>
+        <v>0.7438443401923386</v>
       </c>
       <c r="G7" t="n">
-        <v>30.52365026114555</v>
+        <v>31.05023906410088</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40069073253201</v>
+        <v>34.21683964884757</v>
       </c>
       <c r="I7" t="n">
-        <v>3.194694272040733</v>
+        <v>4.105001150543894</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674006893007068</v>
+        <v>4.649027126202116</v>
       </c>
       <c r="K7" t="n">
-        <v>16.66582040561686</v>
+        <v>14.70662562502468</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21544626765168</v>
+        <v>42.90204158304368</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89364609683393</v>
+        <v>99.86338579401901</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.10372033067129</v>
+        <v>83.88347953899547</v>
       </c>
       <c r="C8" t="n">
-        <v>43.27553296930783</v>
+        <v>41.48275066208854</v>
       </c>
       <c r="D8" t="n">
-        <v>2.00827426794798</v>
+        <v>1.959980921099294</v>
       </c>
       <c r="E8" t="n">
-        <v>9.592617714885399</v>
+        <v>8.796193375544798</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494198063674514</v>
+        <v>0.7448568684964725</v>
       </c>
       <c r="G8" t="n">
-        <v>31.01657646200822</v>
+        <v>30.03818622917832</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47331109290275</v>
+        <v>34.26341595083773</v>
       </c>
       <c r="I8" t="n">
-        <v>5.57964719676293</v>
+        <v>3.425490765735921</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683873789796571</v>
+        <v>4.655355428102953</v>
       </c>
       <c r="K8" t="n">
-        <v>11.8962796693287</v>
+        <v>16.11652046100451</v>
       </c>
       <c r="L8" t="n">
-        <v>44.64259091827235</v>
+        <v>42.2867010671696</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81440355690889</v>
+        <v>99.88597219026265</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.09167689790695</v>
+        <v>82.25707857424166</v>
       </c>
       <c r="C9" t="n">
-        <v>42.1297958179951</v>
+        <v>40.38857903591725</v>
       </c>
       <c r="D9" t="n">
-        <v>1.916911212531128</v>
+        <v>1.884019230989619</v>
       </c>
       <c r="E9" t="n">
-        <v>9.932566382364923</v>
+        <v>8.931598691921668</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507714145114059</v>
+        <v>0.7457194944404816</v>
       </c>
       <c r="G9" t="n">
-        <v>29.6055295550362</v>
+        <v>28.87401602260417</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53548506752466</v>
+        <v>34.30309674426216</v>
       </c>
       <c r="I9" t="n">
-        <v>4.658091925242364</v>
+        <v>2.857881549770555</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692321340696286</v>
+        <v>4.660746840253011</v>
       </c>
       <c r="K9" t="n">
-        <v>13.90832310209306</v>
+        <v>17.74292142575835</v>
       </c>
       <c r="L9" t="n">
-        <v>43.80689088000177</v>
+        <v>41.77334701705395</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84500980008991</v>
+        <v>99.90484747872955</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.96699356082704</v>
+        <v>86.64417660422485</v>
       </c>
       <c r="C10" t="n">
-        <v>40.72805243920297</v>
+        <v>43.35688696755425</v>
       </c>
       <c r="D10" t="n">
-        <v>1.821471081412577</v>
+        <v>1.886205872304868</v>
       </c>
       <c r="E10" t="n">
-        <v>10.08599451396809</v>
+        <v>10.65583076872044</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519301236557216</v>
+        <v>0.7465849957205687</v>
       </c>
       <c r="G10" t="n">
-        <v>28.13151468982194</v>
+        <v>30.11858645215597</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58878568816318</v>
+        <v>35.55396830493541</v>
       </c>
       <c r="I10" t="n">
-        <v>3.887734190957264</v>
+        <v>3.016843987134034</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699563272848259</v>
+        <v>4.666156223253555</v>
       </c>
       <c r="K10" t="n">
-        <v>16.03300643917296</v>
+        <v>13.35582339577516</v>
       </c>
       <c r="L10" t="n">
-        <v>43.10954967925625</v>
+        <v>43.18684474935985</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87060855763218</v>
+        <v>99.89955511268926</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.54130024776218</v>
+        <v>86.60965835494352</v>
       </c>
       <c r="C11" t="n">
-        <v>38.90518017787087</v>
+        <v>43.71232737391796</v>
       </c>
       <c r="D11" t="n">
-        <v>1.713389562234372</v>
+        <v>1.878945930832614</v>
       </c>
       <c r="E11" t="n">
-        <v>10.02819608444374</v>
+        <v>11.08321197793553</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529272942702667</v>
+        <v>0.7473181828611233</v>
       </c>
       <c r="G11" t="n">
-        <v>26.46226126302473</v>
+        <v>30.04577916926468</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63465553643226</v>
+        <v>35.63200235839834</v>
       </c>
       <c r="I11" t="n">
-        <v>3.244074918167634</v>
+        <v>2.551662092769199</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705795589189166</v>
+        <v>4.670738642882021</v>
       </c>
       <c r="K11" t="n">
-        <v>18.45869975223782</v>
+        <v>13.39034164505648</v>
       </c>
       <c r="L11" t="n">
-        <v>42.52812745347583</v>
+        <v>42.81235902502343</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89200738358453</v>
+        <v>99.91502804399786</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.07743849491035</v>
+        <v>85.03706542984986</v>
       </c>
       <c r="C12" t="n">
-        <v>36.94347841197791</v>
+        <v>42.53705984868489</v>
       </c>
       <c r="D12" t="n">
-        <v>1.604717444746846</v>
+        <v>1.811752055172406</v>
       </c>
       <c r="E12" t="n">
-        <v>9.843235489251386</v>
+        <v>11.04155313751876</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7537862761600772</v>
+        <v>0.7479416019364862</v>
       </c>
       <c r="G12" t="n">
-        <v>24.78388640400497</v>
+        <v>28.97129782497236</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67416870336353</v>
+        <v>35.6617268726321</v>
       </c>
       <c r="I12" t="n">
-        <v>2.706479951383064</v>
+        <v>2.128158925514712</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711164226000482</v>
+        <v>4.67463501210304</v>
       </c>
       <c r="K12" t="n">
-        <v>20.92256150508963</v>
+        <v>14.96293457015015</v>
       </c>
       <c r="L12" t="n">
-        <v>42.04384689076112</v>
+        <v>42.42912607858803</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90988680782867</v>
+        <v>99.92912049742307</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.67908905807059</v>
+        <v>86.29357486408422</v>
       </c>
       <c r="C13" t="n">
-        <v>34.96317617057116</v>
+        <v>43.56895839115895</v>
       </c>
       <c r="D13" t="n">
-        <v>1.499964573861444</v>
+        <v>1.813145475350028</v>
       </c>
       <c r="E13" t="n">
-        <v>9.576956899034805</v>
+        <v>11.71455643354336</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754526051086965</v>
+        <v>0.7485168445127791</v>
       </c>
       <c r="G13" t="n">
-        <v>23.1660419286327</v>
+        <v>29.32624856385938</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70819835000037</v>
+        <v>36.02182322667399</v>
       </c>
       <c r="I13" t="n">
-        <v>2.257613436160775</v>
+        <v>1.991054041939817</v>
       </c>
       <c r="J13" t="n">
-        <v>4.71578781929353</v>
+        <v>4.678230278204871</v>
       </c>
       <c r="K13" t="n">
-        <v>23.32091094192941</v>
+        <v>13.70642513591578</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6407328888499</v>
+        <v>42.65829900968279</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92482000135047</v>
+        <v>99.93368253675753</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.54997291231903</v>
+        <v>84.7402536464249</v>
       </c>
       <c r="C14" t="n">
-        <v>39.15937650376276</v>
+        <v>42.32568138320899</v>
       </c>
       <c r="D14" t="n">
-        <v>1.501784537137961</v>
+        <v>1.748565870959542</v>
       </c>
       <c r="E14" t="n">
-        <v>11.92548118203703</v>
+        <v>11.57402978200833</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554415458446971</v>
+        <v>0.7490056948367491</v>
       </c>
       <c r="G14" t="n">
-        <v>25.0241827790027</v>
+        <v>28.28172259710235</v>
       </c>
       <c r="H14" t="n">
-        <v>36.58034373166716</v>
+        <v>36.04534878936966</v>
       </c>
       <c r="I14" t="n">
-        <v>3.041229475100137</v>
+        <v>1.660295319418593</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721509661529355</v>
+        <v>4.681285592729683</v>
       </c>
       <c r="K14" t="n">
-        <v>16.45002708768096</v>
+        <v>15.25974635357509</v>
       </c>
       <c r="L14" t="n">
-        <v>44.28934494491806</v>
+        <v>42.35926520649538</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89874853636178</v>
+        <v>99.94469294327945</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.80435516589769</v>
+        <v>84.1311773707102</v>
       </c>
       <c r="C15" t="n">
-        <v>38.88366528025382</v>
+        <v>41.96199425471592</v>
       </c>
       <c r="D15" t="n">
-        <v>1.474167183948042</v>
+        <v>1.723293325435606</v>
       </c>
       <c r="E15" t="n">
-        <v>12.12899962741993</v>
+        <v>11.63954478138834</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562130489489157</v>
+        <v>0.7494202069557171</v>
       </c>
       <c r="G15" t="n">
-        <v>24.56399579677828</v>
+        <v>27.8729584014256</v>
       </c>
       <c r="H15" t="n">
-        <v>36.61770181568782</v>
+        <v>36.06529688056392</v>
       </c>
       <c r="I15" t="n">
-        <v>2.536946137183965</v>
+        <v>1.396787481467777</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726331555930721</v>
+        <v>4.683876293473233</v>
       </c>
       <c r="K15" t="n">
-        <v>17.19564483410233</v>
+        <v>15.86882262928981</v>
       </c>
       <c r="L15" t="n">
-        <v>43.83621128911329</v>
+        <v>42.12264928586863</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91552140346943</v>
+        <v>99.95346616987436</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.51187610171097</v>
+        <v>82.15417311380614</v>
       </c>
       <c r="C16" t="n">
-        <v>36.98325022307289</v>
+        <v>40.20221071961618</v>
       </c>
       <c r="D16" t="n">
-        <v>1.386836426136012</v>
+        <v>1.641447169881513</v>
       </c>
       <c r="E16" t="n">
-        <v>11.76313099945607</v>
+        <v>11.28082574619457</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568755296992967</v>
+        <v>0.749774309265711</v>
       </c>
       <c r="G16" t="n">
-        <v>23.10880645924398</v>
+        <v>26.54915910654978</v>
       </c>
       <c r="H16" t="n">
-        <v>36.6497807683187</v>
+        <v>36.08233779408278</v>
       </c>
       <c r="I16" t="n">
-        <v>2.115973858236311</v>
+        <v>1.164539554921085</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730472060620603</v>
+        <v>4.686089432910695</v>
       </c>
       <c r="K16" t="n">
-        <v>19.48812389828905</v>
+        <v>17.84582688619387</v>
       </c>
       <c r="L16" t="n">
-        <v>43.45815515260517</v>
+        <v>41.91316274192697</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92952927396712</v>
+        <v>99.96120034773701</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.1751923321541</v>
+        <v>86.17227993522452</v>
       </c>
       <c r="C17" t="n">
-        <v>38.19552706912143</v>
+        <v>42.80418348504811</v>
       </c>
       <c r="D17" t="n">
-        <v>1.388027379485003</v>
+        <v>1.642321979564388</v>
       </c>
       <c r="E17" t="n">
-        <v>12.54009907999933</v>
+        <v>12.69382858663251</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575255006907397</v>
+        <v>0.7501739016727967</v>
       </c>
       <c r="G17" t="n">
-        <v>23.54267572625217</v>
+        <v>27.74067151755454</v>
       </c>
       <c r="H17" t="n">
-        <v>37.09527842090871</v>
+        <v>37.27893091507167</v>
       </c>
       <c r="I17" t="n">
-        <v>2.117051845501007</v>
+        <v>1.377766149273645</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734534379317121</v>
+        <v>4.68858688545498</v>
       </c>
       <c r="K17" t="n">
-        <v>17.82480766784594</v>
+        <v>13.82772006477547</v>
       </c>
       <c r="L17" t="n">
-        <v>43.90915741718001</v>
+        <v>43.32219537485695</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92949215414737</v>
+        <v>99.95409892468054</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.94797003786861</v>
+        <v>87.7879912194887</v>
       </c>
       <c r="C18" t="n">
-        <v>36.29514037068361</v>
+        <v>43.54976785950048</v>
       </c>
       <c r="D18" t="n">
-        <v>1.306485600979036</v>
+        <v>1.643693444918877</v>
       </c>
       <c r="E18" t="n">
-        <v>12.09766331574992</v>
+        <v>13.30886209848199</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580831207379615</v>
+        <v>0.7508003546636156</v>
       </c>
       <c r="G18" t="n">
-        <v>22.15962545081732</v>
+        <v>27.88277937206467</v>
       </c>
       <c r="H18" t="n">
-        <v>37.12258452596512</v>
+        <v>37.31006169383404</v>
       </c>
       <c r="I18" t="n">
-        <v>1.765508519007013</v>
+        <v>2.19929203887793</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738019504612257</v>
+        <v>4.692502216647598</v>
       </c>
       <c r="K18" t="n">
-        <v>20.05202996213138</v>
+        <v>12.21200878051129</v>
       </c>
       <c r="L18" t="n">
-        <v>43.59402267147667</v>
+        <v>44.164974793554</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94119300429166</v>
+        <v>99.92675143356577</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.06408294478115</v>
+        <v>85.56994826623796</v>
       </c>
       <c r="C19" t="n">
-        <v>35.6831799117255</v>
+        <v>41.67354954450035</v>
       </c>
       <c r="D19" t="n">
-        <v>1.274805494146095</v>
+        <v>1.55969539590406</v>
       </c>
       <c r="E19" t="n">
-        <v>12.04967677414006</v>
+        <v>12.93441167861994</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758553636713337</v>
+        <v>0.7513367608403791</v>
       </c>
       <c r="G19" t="n">
-        <v>21.62229132242448</v>
+        <v>26.45787920250805</v>
       </c>
       <c r="H19" t="n">
-        <v>37.14562523032705</v>
+        <v>37.33671771154059</v>
       </c>
       <c r="I19" t="n">
-        <v>1.472170257571779</v>
+        <v>1.834052761572585</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740960229458354</v>
+        <v>4.69585475525237</v>
       </c>
       <c r="K19" t="n">
-        <v>20.93591705521887</v>
+        <v>14.43005173376202</v>
       </c>
       <c r="L19" t="n">
-        <v>43.33186112974988</v>
+        <v>43.83530727621324</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95095809669424</v>
+        <v>99.93890855447562</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.63556310121693</v>
+        <v>83.2395246532821</v>
       </c>
       <c r="C20" t="n">
-        <v>33.48127547518917</v>
+        <v>39.62762897513498</v>
       </c>
       <c r="D20" t="n">
-        <v>1.186850076733425</v>
+        <v>1.471839818033841</v>
       </c>
       <c r="E20" t="n">
-        <v>11.42288457410357</v>
+        <v>12.46071893385561</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589586257688854</v>
+        <v>0.7517968905313603</v>
       </c>
       <c r="G20" t="n">
-        <v>20.13045773101368</v>
+        <v>24.96754187596267</v>
       </c>
       <c r="H20" t="n">
-        <v>37.16545714589859</v>
+        <v>37.3595832670122</v>
       </c>
       <c r="I20" t="n">
-        <v>1.227463536643251</v>
+        <v>1.52931330206542</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743491411055532</v>
+        <v>4.698730565821002</v>
       </c>
       <c r="K20" t="n">
-        <v>23.36443689878308</v>
+        <v>16.76047534671789</v>
       </c>
       <c r="L20" t="n">
-        <v>43.11339400776188</v>
+        <v>43.56094976810344</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95910638173413</v>
+        <v>99.94905408995631</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.18294813901761</v>
+        <v>80.88249567754116</v>
       </c>
       <c r="C21" t="n">
-        <v>36.86322624761313</v>
+        <v>37.5072731679294</v>
       </c>
       <c r="D21" t="n">
-        <v>1.18772671121919</v>
+        <v>1.383384902179112</v>
       </c>
       <c r="E21" t="n">
-        <v>13.26635727902472</v>
+        <v>11.92436846468194</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595192098878578</v>
+        <v>0.7521919551223653</v>
       </c>
       <c r="G21" t="n">
-        <v>21.67685106559312</v>
+        <v>23.46703768476072</v>
       </c>
       <c r="H21" t="n">
-        <v>38.72443291885406</v>
+        <v>37.37921549570241</v>
       </c>
       <c r="I21" t="n">
-        <v>1.821065892639563</v>
+        <v>1.275097455579819</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746995061799109</v>
+        <v>4.701199719514783</v>
       </c>
       <c r="K21" t="n">
-        <v>17.81705186098239</v>
+        <v>19.11750432245884</v>
       </c>
       <c r="L21" t="n">
-        <v>45.25906449791488</v>
+        <v>43.33274158455439</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93934260651041</v>
+        <v>99.95751907494264</v>
       </c>
     </row>
   </sheetData>
